--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:41</t>
+    <t xml:space="preserve">2026-09-10 00:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:49</t>
+    <t xml:space="preserve">2026-09-18 10:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:58</t>
+    <t xml:space="preserve">2026-09-23 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:19</t>
+    <t xml:space="preserve">2026-10-02 15:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:26</t>
+    <t xml:space="preserve">2026-10-04 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:01</t>
+    <t xml:space="preserve">2026-10-05 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
